--- a/Carga_Real_FRAM Apply-Actualizado 28-11.xlsx
+++ b/Carga_Real_FRAM Apply-Actualizado 28-11.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7831" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7817" uniqueCount="1199">
   <si>
     <t xml:space="preserve">Activo</t>
   </si>
@@ -1772,6 +1772,9 @@
     <t xml:space="preserve"> 17:05 19:25</t>
   </si>
   <si>
+    <t xml:space="preserve">AUTOGESTION SCL</t>
+  </si>
+  <si>
     <t xml:space="preserve">16-45</t>
   </si>
   <si>
@@ -1814,246 +1817,246 @@
     <t xml:space="preserve"> 23:35</t>
   </si>
   <si>
+    <t xml:space="preserve">IRPAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARDIANSYAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5596554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United Airlines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UA7916 CGK NRT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06:20 15:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UA6 NRT IAH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:45 14:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UA847 IAH SCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:15 08:50+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHISHEK VIJAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JADHAV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N4250413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EK501 BOM DXB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:15 06:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EK201 DXB JKF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:30 13:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERIC JOHN OBISPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERALTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chef De Cuisine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P0687833B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippine Airlines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">American Airlines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PR112 MNL-LAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:20 08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AA658 LAX-MIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:31 20:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AA957 MIA-SCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:45 09:00+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RIZALINO JR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAQUIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P8070138B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QR929 MNL-DOH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:50 04:50+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QR151 DOH-MAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:20 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QR5354 MAD SCL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:59 09:20+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARK JULIUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAUTISTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P9280329A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WILFEDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANAOG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3298512B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:20 04:20+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:05 18:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23:20 09:50+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:29 18:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEPHEN REY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PETRACORTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheft de Partie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P8210472B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHILIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOUTHIVEI RAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beautician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3935229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TK721 BOM-IST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:00 11:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:54 13:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARTER PUQ WPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JIMENEA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOEMEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Able Seaman/Zodiac Drive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P7487860B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TK85 MNL IST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:35 05:45+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TK903 IST - PTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:50 20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TK9608 PTY - SCL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:31 05:54+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA83 SCL - PUQ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUKAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCHNERMANN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1Y8VTTGJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KL1802  DUS AMS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:30 15:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21:20 10:50+1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:43 23:09</t>
+  </si>
+  <si>
     <t xml:space="preserve">AUTOGESTION</t>
   </si>
   <si>
-    <t xml:space="preserve">IRPAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARDIANSYAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E5596554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United Airlines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UA7916 CGK NRT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06:20 15:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UA6 NRT IAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:45 14:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UA847 IAH SCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:15 08:50+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHISHEK VIJAY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JADHAV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N4250413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EK501 BOM DXB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:15 06:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EK201 DXB JKF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08:30 13:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERIC JOHN OBISPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PERALTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chef De Cuisine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P0687833B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippine Airlines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">American Airlines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PR112 MNL-LAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:20 08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AA658 LAX-MIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:31 20:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AA957 MIA-SCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:45 09:00+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RIZALINO JR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOAQUIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P8070138B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QR929 MNL-DOH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:50 04:50+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QR151 DOH-MAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:20 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QR5354 MAD SCL </t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:59 09:20+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARK JULIUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAUTISTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P9280329A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WILFEDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANAOG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Butcher</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P3298512B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:20 04:20+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:05 18:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23:20 09:50+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:29 18:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEPHEN REY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PETRACORTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheft de Partie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P8210472B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHILIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOUTHIVEI RAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beautician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R3935229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TK721 BOM-IST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:00 11:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:54 13:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHARTER PUQ WPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JIMENEA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOEMEL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Able Seaman/Zodiac Drive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P7487860B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TK85 MNL IST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:35 05:45+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TK903 IST - PTY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:50 20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TK9608 PTY - SCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:31 05:54+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LA83 SCL - PUQ  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUKAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCHNERMANN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1Y8VTTGJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KL1802  DUS AMS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:30 15:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21:20 10:50+1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19:43 23:09</t>
-  </si>
-  <si>
     <t xml:space="preserve">MARANA</t>
   </si>
   <si>
@@ -2201,9 +2204,6 @@
     <t xml:space="preserve">LA91 SCL PUQ</t>
   </si>
   <si>
-    <t xml:space="preserve">4:32 7:56</t>
-  </si>
-  <si>
     <t xml:space="preserve">DAP PUQ WPU</t>
   </si>
   <si>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">LA93 SCL PUQ</t>
   </si>
   <si>
-    <t xml:space="preserve">5:44 9:10</t>
+    <t xml:space="preserve">05:44 09:10</t>
   </si>
   <si>
     <t xml:space="preserve">Joward</t>
@@ -3641,7 +3641,7 @@
     <numFmt numFmtId="174" formatCode="@"/>
     <numFmt numFmtId="175" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3730,14 +3730,6 @@
       <sz val="8"/>
       <color rgb="FFC9211E"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -3856,7 +3848,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="140">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4369,10 +4361,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="170" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4417,7 +4405,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4668,7 +4656,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="4" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="7.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="11.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="14.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="2" width="8.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="2" width="9.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="7.44"/>
@@ -13705,7 +13693,7 @@
       <c r="DA38" s="38"/>
       <c r="DB38" s="37"/>
     </row>
-    <row r="39" s="43" customFormat="true" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" s="43" customFormat="true" ht="10.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="36" t="s">
         <v>106</v>
       </c>
@@ -13803,17 +13791,11 @@
       <c r="AO39" s="38"/>
       <c r="AP39" s="37"/>
       <c r="AQ39" s="37"/>
-      <c r="AR39" s="37" t="s">
-        <v>147</v>
-      </c>
+      <c r="AR39" s="37"/>
       <c r="AS39" s="37"/>
-      <c r="AT39" s="37" t="s">
-        <v>147</v>
-      </c>
+      <c r="AT39" s="37"/>
       <c r="AU39" s="37"/>
-      <c r="AV39" s="37" t="s">
-        <v>147</v>
-      </c>
+      <c r="AV39" s="37"/>
       <c r="AW39" s="37" t="n">
         <v>3</v>
       </c>
@@ -18764,7 +18746,9 @@
       <c r="BB60" s="61" t="s">
         <v>160</v>
       </c>
-      <c r="BC60" s="61"/>
+      <c r="BC60" s="68" t="s">
+        <v>582</v>
+      </c>
       <c r="BD60" s="38" t="n">
         <v>45610</v>
       </c>
@@ -18814,7 +18798,7 @@
         <v>45613</v>
       </c>
       <c r="BX60" s="67" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="BY60" s="61" t="s">
         <v>140</v>
@@ -18898,28 +18882,28 @@
         <v>111</v>
       </c>
       <c r="K61" s="63" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L61" s="63" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N61" s="61" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O61" s="61" t="s">
         <v>408</v>
       </c>
       <c r="P61" s="61" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="Q61" s="40" t="n">
         <v>29004</v>
       </c>
       <c r="R61" s="63" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="S61" s="63" t="s">
         <v>118</v>
@@ -18931,31 +18915,31 @@
         <v>119</v>
       </c>
       <c r="V61" s="63" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="W61" s="62" t="n">
         <v>45608</v>
       </c>
       <c r="X61" s="62" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Y61" s="61" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z61" s="62" t="n">
         <v>45608</v>
       </c>
       <c r="AA61" s="61" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AB61" s="61" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AC61" s="62" t="n">
         <v>45609</v>
       </c>
       <c r="AD61" s="61" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AE61" s="61" t="s">
         <v>542</v>
@@ -18964,7 +18948,7 @@
         <v>45609</v>
       </c>
       <c r="AG61" s="61" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AH61" s="63" t="s">
         <v>542</v>
@@ -18973,7 +18957,7 @@
         <v>45609</v>
       </c>
       <c r="AJ61" s="41" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AK61" s="65" t="s">
         <v>416</v>
@@ -19028,7 +19012,7 @@
         <v>160</v>
       </c>
       <c r="BC61" s="68" t="s">
-        <v>596</v>
+        <v>582</v>
       </c>
       <c r="BD61" s="38" t="n">
         <v>45610</v>
@@ -19079,7 +19063,7 @@
         <v>45613</v>
       </c>
       <c r="BX61" s="67" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="BY61" s="61" t="s">
         <v>140</v>
@@ -21338,7 +21322,7 @@
         <v>160</v>
       </c>
       <c r="BC71" s="69" t="s">
-        <v>596</v>
+        <v>676</v>
       </c>
       <c r="BD71" s="38" t="n">
         <v>45610</v>
@@ -21451,10 +21435,10 @@
         <v>111</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="L72" s="5" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>150</v>
@@ -21466,7 +21450,7 @@
         <v>482</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="Q72" s="40" t="n">
         <v>34620</v>
@@ -21586,22 +21570,22 @@
         <v>111</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L73" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O73" s="1" t="s">
         <v>151</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="Q73" s="40" t="n">
         <v>32171</v>
@@ -21625,7 +21609,7 @@
         <v>45610</v>
       </c>
       <c r="X73" s="62" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="Y73" s="1" t="s">
         <v>205</v>
@@ -21783,10 +21767,10 @@
         <v>111</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="L74" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>150</v>
@@ -21795,10 +21779,10 @@
         <v>309</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="Q74" s="40" t="n">
         <v>30060</v>
@@ -21989,10 +21973,10 @@
         <v>111</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="L75" s="5" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>150</v>
@@ -22004,7 +21988,7 @@
         <v>408</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="Q75" s="40" t="n">
         <v>31545</v>
@@ -22169,10 +22153,10 @@
         <v>111</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="L76" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>150</v>
@@ -22184,7 +22168,7 @@
         <v>369</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="Q76" s="40" t="n">
         <v>45486</v>
@@ -22211,13 +22195,13 @@
         <v>663</v>
       </c>
       <c r="Y76" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="Z76" s="4" t="n">
         <v>45610</v>
       </c>
       <c r="AA76" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AB76" s="1" t="s">
         <v>666</v>
@@ -22375,22 +22359,22 @@
         <v>111</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="L77" s="5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O77" s="1" t="s">
         <v>294</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Q77" s="40" t="n">
         <v>34125</v>
@@ -22408,16 +22392,16 @@
         <v>120</v>
       </c>
       <c r="V77" s="5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="W77" s="4" t="n">
         <v>45613</v>
       </c>
       <c r="X77" s="62" t="s">
+        <v>701</v>
+      </c>
+      <c r="AH77" s="5" t="s">
         <v>700</v>
-      </c>
-      <c r="AH77" s="5" t="s">
-        <v>699</v>
       </c>
       <c r="AI77" s="4" t="n">
         <v>45613</v>
@@ -22426,13 +22410,13 @@
         <v>0.614583333333333</v>
       </c>
       <c r="AK77" s="65" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AL77" s="38" t="n">
         <v>45614</v>
       </c>
       <c r="AM77" s="66" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AN77" s="46" t="s">
         <v>566</v>
@@ -22514,10 +22498,10 @@
         <v>111</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="L78" s="5" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>150</v>
@@ -22529,7 +22513,7 @@
         <v>425</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="Q78" s="40" t="n">
         <v>35061</v>
@@ -22630,10 +22614,10 @@
         <v>111</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L79" s="5" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>150</v>
@@ -22642,10 +22626,10 @@
         <v>195</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="Q79" s="40" t="n">
         <v>29216</v>
@@ -22663,16 +22647,16 @@
         <v>120</v>
       </c>
       <c r="V79" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="W79" s="4" t="n">
         <v>45613</v>
       </c>
       <c r="X79" s="62" t="s">
+        <v>712</v>
+      </c>
+      <c r="AH79" s="5" t="s">
         <v>711</v>
-      </c>
-      <c r="AH79" s="5" t="s">
-        <v>710</v>
       </c>
       <c r="AI79" s="4" t="n">
         <v>45613</v>
@@ -22754,10 +22738,10 @@
         <v>111</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="L80" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>150</v>
@@ -22769,7 +22753,7 @@
         <v>116</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="Q80" s="40" t="n">
         <v>29317</v>
@@ -22862,10 +22846,10 @@
         <v>111</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="L81" s="5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>150</v>
@@ -22874,10 +22858,10 @@
         <v>195</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q81" s="40" t="n">
         <v>33365</v>
@@ -22892,13 +22876,13 @@
         <v>120</v>
       </c>
       <c r="V81" s="5" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="W81" s="4" t="n">
         <v>45623</v>
       </c>
       <c r="X81" s="62" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="Y81" s="1" t="s">
         <v>442</v>
@@ -22907,19 +22891,19 @@
         <v>45623</v>
       </c>
       <c r="AA81" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AB81" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AC81" s="4" t="n">
         <v>45623</v>
       </c>
       <c r="AD81" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="AH81" s="5" t="s">
         <v>723</v>
-      </c>
-      <c r="AH81" s="5" t="s">
-        <v>722</v>
       </c>
       <c r="AI81" s="4" t="n">
         <v>45624</v>
@@ -22928,13 +22912,13 @@
         <v>0.0590277777777778</v>
       </c>
       <c r="AK81" s="65" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AL81" s="38" t="n">
         <v>45624</v>
       </c>
       <c r="AM81" s="66" t="s">
-        <v>725</v>
+        <v>224</v>
       </c>
       <c r="AN81" s="73" t="s">
         <v>726</v>
@@ -23095,13 +23079,13 @@
         <v>120</v>
       </c>
       <c r="V82" s="5" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="W82" s="4" t="n">
         <v>45623</v>
       </c>
       <c r="X82" s="62" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="Y82" s="1" t="s">
         <v>442</v>
@@ -23110,7 +23094,7 @@
         <v>45623</v>
       </c>
       <c r="AA82" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AB82" s="1" t="s">
         <v>205</v>
@@ -23280,7 +23264,7 @@
         <v>195</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P83" s="72" t="s">
         <v>735</v>
@@ -25140,16 +25124,16 @@
         <v>807</v>
       </c>
       <c r="AB92" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AC92" s="4" t="n">
         <v>45622</v>
       </c>
       <c r="AD92" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="AH92" s="5" t="s">
         <v>723</v>
-      </c>
-      <c r="AH92" s="5" t="s">
-        <v>722</v>
       </c>
       <c r="AI92" s="4" t="n">
         <v>45623</v>
@@ -25922,16 +25906,9 @@
       <c r="AM96" s="66"/>
       <c r="AN96" s="73"/>
       <c r="AQ96" s="61"/>
-      <c r="AR96" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="AT96" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="AR96" s="61"/>
       <c r="AU96" s="61"/>
-      <c r="AV96" s="61" t="s">
-        <v>147</v>
-      </c>
+      <c r="AV96" s="61"/>
       <c r="AW96" s="3" t="n">
         <v>3</v>
       </c>
@@ -26010,17 +25987,11 @@
       <c r="AO97" s="77"/>
       <c r="AP97" s="83"/>
       <c r="AQ97" s="84"/>
-      <c r="AR97" s="84" t="s">
-        <v>147</v>
-      </c>
+      <c r="AR97" s="84"/>
       <c r="AS97" s="74"/>
-      <c r="AT97" s="74" t="s">
-        <v>147</v>
-      </c>
+      <c r="AT97" s="74"/>
       <c r="AU97" s="84"/>
-      <c r="AV97" s="84" t="s">
-        <v>147</v>
-      </c>
+      <c r="AV97" s="84"/>
       <c r="AW97" s="85" t="n">
         <v>3</v>
       </c>
@@ -26128,16 +26099,9 @@
       <c r="AM98" s="66"/>
       <c r="AN98" s="73"/>
       <c r="AQ98" s="61"/>
-      <c r="AR98" s="61" t="s">
-        <v>147</v>
-      </c>
-      <c r="AT98" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="AR98" s="61"/>
       <c r="AU98" s="61"/>
-      <c r="AV98" s="61" t="s">
-        <v>147</v>
-      </c>
+      <c r="AV98" s="61"/>
       <c r="AW98" s="3" t="n">
         <v>3</v>
       </c>
@@ -26215,17 +26179,11 @@
       <c r="AO99" s="77"/>
       <c r="AP99" s="83"/>
       <c r="AQ99" s="84"/>
-      <c r="AR99" s="84" t="s">
-        <v>147</v>
-      </c>
+      <c r="AR99" s="84"/>
       <c r="AS99" s="74"/>
-      <c r="AT99" s="74" t="s">
-        <v>147</v>
-      </c>
+      <c r="AT99" s="74"/>
       <c r="AU99" s="84"/>
-      <c r="AV99" s="84" t="s">
-        <v>147</v>
-      </c>
+      <c r="AV99" s="84"/>
       <c r="AW99" s="85" t="n">
         <v>3</v>
       </c>
@@ -26322,7 +26280,7 @@
         <v>846</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="P100" s="1" t="s">
         <v>847</v>
@@ -26355,19 +26313,19 @@
         <v>45623</v>
       </c>
       <c r="AA100" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AB100" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AC100" s="4" t="n">
         <v>45623</v>
       </c>
       <c r="AD100" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="AH100" s="5" t="s">
         <v>723</v>
-      </c>
-      <c r="AH100" s="5" t="s">
-        <v>722</v>
       </c>
       <c r="AI100" s="4" t="n">
         <v>45624</v>
@@ -27707,7 +27665,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="12.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="8.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="9" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="7"/>
@@ -38043,7 +38001,7 @@
       <c r="BP53" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="BQ53" s="128" t="n">
+      <c r="BQ53" s="62" t="n">
         <v>45616</v>
       </c>
       <c r="BR53" s="67" t="n">
@@ -39223,10 +39181,10 @@
         <v>398</v>
       </c>
       <c r="D61" s="86"/>
-      <c r="E61" s="129" t="n">
+      <c r="E61" s="128" t="n">
         <v>45615</v>
       </c>
-      <c r="F61" s="129" t="n">
+      <c r="F61" s="128" t="n">
         <v>45615</v>
       </c>
       <c r="G61" s="49" t="s">
@@ -39241,7 +39199,7 @@
       <c r="J61" s="74" t="s">
         <v>106</v>
       </c>
-      <c r="K61" s="130" t="s">
+      <c r="K61" s="129" t="s">
         <v>1114</v>
       </c>
       <c r="L61" s="76" t="s">
@@ -39250,16 +39208,16 @@
       <c r="M61" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="N61" s="130" t="s">
+      <c r="N61" s="129" t="s">
         <v>195</v>
       </c>
-      <c r="O61" s="130" t="s">
-        <v>708</v>
-      </c>
-      <c r="P61" s="130" t="s">
+      <c r="O61" s="129" t="s">
+        <v>709</v>
+      </c>
+      <c r="P61" s="129" t="s">
         <v>1116</v>
       </c>
-      <c r="Q61" s="129" t="n">
+      <c r="Q61" s="128" t="n">
         <v>35127</v>
       </c>
       <c r="R61" s="58" t="s">
@@ -39277,16 +39235,16 @@
       <c r="W61" s="86" t="n">
         <v>45615</v>
       </c>
-      <c r="X61" s="131" t="s">
+      <c r="X61" s="130" t="s">
         <v>1018</v>
       </c>
-      <c r="Y61" s="130" t="s">
+      <c r="Y61" s="129" t="s">
         <v>941</v>
       </c>
       <c r="Z61" s="86" t="n">
         <v>45615</v>
       </c>
-      <c r="AA61" s="132" t="n">
+      <c r="AA61" s="131" t="n">
         <v>0.999305555555556</v>
       </c>
       <c r="AB61" s="58" t="s">
@@ -39295,19 +39253,19 @@
       <c r="AC61" s="77" t="n">
         <v>45616</v>
       </c>
-      <c r="AD61" s="133" t="n">
+      <c r="AD61" s="132" t="n">
         <v>0.263888888888889</v>
       </c>
       <c r="AE61" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="AF61" s="134" t="s">
+      <c r="AF61" s="133" t="s">
         <v>872</v>
       </c>
       <c r="AG61" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="AH61" s="134" t="s">
+      <c r="AH61" s="133" t="s">
         <v>873</v>
       </c>
       <c r="AI61" s="50" t="s">
@@ -39316,15 +39274,15 @@
       <c r="AJ61" s="87" t="s">
         <v>874</v>
       </c>
-      <c r="AK61" s="135" t="n">
+      <c r="AK61" s="134" t="n">
         <v>3</v>
       </c>
-      <c r="AM61" s="136"/>
-      <c r="AN61" s="136"/>
-      <c r="AR61" s="136"/>
-      <c r="AS61" s="136"/>
-      <c r="AW61" s="136"/>
-      <c r="AX61" s="136"/>
+      <c r="AM61" s="135"/>
+      <c r="AN61" s="135"/>
+      <c r="AR61" s="135"/>
+      <c r="AS61" s="135"/>
+      <c r="AW61" s="135"/>
+      <c r="AX61" s="135"/>
       <c r="BA61" s="84" t="s">
         <v>143</v>
       </c>
@@ -39340,32 +39298,32 @@
       <c r="BE61" s="79" t="n">
         <v>45615</v>
       </c>
-      <c r="BF61" s="137" t="n">
+      <c r="BF61" s="136" t="n">
         <v>0.59375</v>
       </c>
       <c r="BG61" s="84"/>
       <c r="BH61" s="84"/>
       <c r="BI61" s="84"/>
       <c r="BJ61" s="84"/>
-      <c r="BK61" s="138"/>
-      <c r="BL61" s="139"/>
+      <c r="BK61" s="137"/>
+      <c r="BL61" s="138"/>
       <c r="BM61" s="84"/>
       <c r="BN61" s="79"/>
       <c r="BO61" s="84"/>
       <c r="BP61" s="74"/>
       <c r="BQ61" s="79"/>
-      <c r="BR61" s="137"/>
+      <c r="BR61" s="136"/>
       <c r="BS61" s="79"/>
       <c r="BT61" s="79"/>
       <c r="BU61" s="79"/>
       <c r="BV61" s="79"/>
       <c r="BW61" s="79"/>
-      <c r="BX61" s="139"/>
+      <c r="BX61" s="138"/>
       <c r="BY61" s="74"/>
-      <c r="CA61" s="136"/>
-      <c r="CB61" s="136"/>
-      <c r="CE61" s="136"/>
-      <c r="CF61" s="136"/>
+      <c r="CA61" s="135"/>
+      <c r="CB61" s="135"/>
+      <c r="CE61" s="135"/>
+      <c r="CF61" s="135"/>
       <c r="CL61" s="74"/>
       <c r="CM61" s="74"/>
       <c r="CN61" s="74"/>
@@ -39592,7 +39550,7 @@
         <v>150</v>
       </c>
       <c r="N63" s="110" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O63" s="110" t="s">
         <v>116</v>
@@ -39693,7 +39651,7 @@
       <c r="BJ63" s="61" t="s">
         <v>142</v>
       </c>
-      <c r="BK63" s="128" t="n">
+      <c r="BK63" s="62" t="n">
         <v>45616</v>
       </c>
       <c r="BL63" s="67" t="n">
@@ -41007,7 +40965,7 @@
         <v>1165</v>
       </c>
       <c r="O72" s="5" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P72" s="5" t="s">
         <v>1180</v>
@@ -41895,7 +41853,7 @@
       <c r="BP79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="Q80" s="140"/>
+      <c r="Q80" s="139"/>
       <c r="BP80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Carga_Real_FRAM Apply-Actualizado 28-11.xlsx
+++ b/Carga_Real_FRAM Apply-Actualizado 28-11.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7829" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7830" uniqueCount="1200">
   <si>
     <t xml:space="preserve">Activo</t>
   </si>
@@ -2916,6 +2916,9 @@
   </si>
   <si>
     <t xml:space="preserve">P7849992B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-00</t>
   </si>
   <si>
     <t xml:space="preserve">RONNIE GIDOR</t>
@@ -28016,9 +28019,7 @@
       <c r="P2" s="110" t="s">
         <v>859</v>
       </c>
-      <c r="Q2" s="60" t="n">
-        <v>26176</v>
-      </c>
+      <c r="Q2" s="60"/>
       <c r="R2" s="43" t="s">
         <v>120</v>
       </c>
@@ -32355,8 +32356,8 @@
       <c r="BK22" s="9" t="n">
         <v>45614</v>
       </c>
-      <c r="BL22" s="115" t="n">
-        <v>0.416666666666667</v>
+      <c r="BL22" s="115" t="s">
+        <v>964</v>
       </c>
       <c r="BM22" s="61" t="s">
         <v>140</v>
@@ -32445,10 +32446,10 @@
         <v>106</v>
       </c>
       <c r="K23" s="110" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M23" s="36" t="s">
         <v>150</v>
@@ -32460,7 +32461,7 @@
         <v>365</v>
       </c>
       <c r="P23" s="110" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="Q23" s="60" t="n">
         <v>27501</v>
@@ -32496,7 +32497,7 @@
         <v>955</v>
       </c>
       <c r="AB23" s="43" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="AC23" s="9" t="n">
         <v>45615</v>
@@ -32630,10 +32631,10 @@
         <v>106</v>
       </c>
       <c r="K24" s="110" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="M24" s="36" t="s">
         <v>150</v>
@@ -32645,7 +32646,7 @@
         <v>330</v>
       </c>
       <c r="P24" s="110" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="Q24" s="60" t="n">
         <v>29003</v>
@@ -32681,7 +32682,7 @@
         <v>922</v>
       </c>
       <c r="AB24" s="43" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="AC24" s="9" t="n">
         <v>45615</v>
@@ -32861,10 +32862,10 @@
         <v>106</v>
       </c>
       <c r="K25" s="110" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="M25" s="36" t="s">
         <v>150</v>
@@ -32876,7 +32877,7 @@
         <v>616</v>
       </c>
       <c r="P25" s="110" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="Q25" s="60" t="n">
         <v>29012</v>
@@ -33092,10 +33093,10 @@
         <v>106</v>
       </c>
       <c r="K26" s="110" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="M26" s="36" t="s">
         <v>150</v>
@@ -33107,7 +33108,7 @@
         <v>324</v>
       </c>
       <c r="P26" s="110" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="Q26" s="60" t="n">
         <v>30893</v>
@@ -33323,10 +33324,10 @@
         <v>106</v>
       </c>
       <c r="K27" s="110" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="M27" s="36" t="s">
         <v>150</v>
@@ -33338,7 +33339,7 @@
         <v>256</v>
       </c>
       <c r="P27" s="110" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="Q27" s="60" t="n">
         <v>32811</v>
@@ -33545,10 +33546,10 @@
         <v>106</v>
       </c>
       <c r="K28" s="110" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="M28" s="36" t="s">
         <v>150</v>
@@ -33560,7 +33561,7 @@
         <v>338</v>
       </c>
       <c r="P28" s="110" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="Q28" s="60" t="n">
         <v>34913</v>
@@ -33593,7 +33594,7 @@
         <v>45616</v>
       </c>
       <c r="AA28" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB28" s="43" t="s">
         <v>956</v>
@@ -33767,10 +33768,10 @@
         <v>106</v>
       </c>
       <c r="K29" s="110" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="M29" s="36" t="s">
         <v>150</v>
@@ -33782,7 +33783,7 @@
         <v>334</v>
       </c>
       <c r="P29" s="110" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="Q29" s="60" t="n">
         <v>34983</v>
@@ -33809,7 +33810,7 @@
         <v>869</v>
       </c>
       <c r="Y29" s="110" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="Z29" s="9" t="n">
         <v>45615</v>
@@ -33998,10 +33999,10 @@
         <v>106</v>
       </c>
       <c r="K30" s="110" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="M30" s="36" t="s">
         <v>150</v>
@@ -34010,10 +34011,10 @@
         <v>309</v>
       </c>
       <c r="O30" s="43" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="P30" s="110" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="Q30" s="60" t="n">
         <v>23895</v>
@@ -34046,7 +34047,7 @@
         <v>45615</v>
       </c>
       <c r="AA30" s="10" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AB30" s="43" t="s">
         <v>956</v>
@@ -34232,10 +34233,10 @@
         <v>106</v>
       </c>
       <c r="K31" s="110" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="M31" s="36" t="s">
         <v>150</v>
@@ -34247,7 +34248,7 @@
         <v>373</v>
       </c>
       <c r="P31" s="110" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="Q31" s="60" t="n">
         <v>32270</v>
@@ -34274,13 +34275,13 @@
         <v>869</v>
       </c>
       <c r="Y31" s="110" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="Z31" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="AA31" s="10" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AB31" s="43" t="s">
         <v>956</v>
@@ -34467,10 +34468,10 @@
         <v>106</v>
       </c>
       <c r="K32" s="110" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="L32" s="110" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="M32" s="36" t="s">
         <v>150</v>
@@ -34482,7 +34483,7 @@
         <v>359</v>
       </c>
       <c r="P32" s="110" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="Q32" s="60" t="n">
         <v>24881</v>
@@ -34509,7 +34510,7 @@
         <v>908</v>
       </c>
       <c r="Y32" s="110" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="Z32" s="9" t="n">
         <v>45616</v>
@@ -34617,10 +34618,10 @@
         <v>106</v>
       </c>
       <c r="K33" s="110" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L33" s="110" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="M33" s="36" t="s">
         <v>150</v>
@@ -34632,7 +34633,7 @@
         <v>210</v>
       </c>
       <c r="P33" s="110" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="Q33" s="60" t="n">
         <v>32784</v>
@@ -34665,7 +34666,7 @@
         <v>45616</v>
       </c>
       <c r="AA33" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB33" s="43" t="s">
         <v>956</v>
@@ -34840,10 +34841,10 @@
         <v>106</v>
       </c>
       <c r="K34" s="110" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="L34" s="110" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="M34" s="36" t="s">
         <v>150</v>
@@ -34855,7 +34856,7 @@
         <v>379</v>
       </c>
       <c r="P34" s="110" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="Q34" s="60" t="n">
         <v>29907</v>
@@ -34875,7 +34876,7 @@
       <c r="V34" s="43"/>
       <c r="X34" s="123"/>
       <c r="Y34" s="110" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="Z34" s="124"/>
       <c r="AB34" s="43"/>
@@ -34955,10 +34956,10 @@
         <v>106</v>
       </c>
       <c r="K35" s="110" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="L35" s="110" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="M35" s="36" t="s">
         <v>114</v>
@@ -34970,7 +34971,7 @@
         <v>210</v>
       </c>
       <c r="P35" s="110" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="Q35" s="60" t="n">
         <v>25345</v>
@@ -35068,10 +35069,10 @@
         <v>106</v>
       </c>
       <c r="K36" s="110" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="L36" s="110" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="M36" s="36" t="s">
         <v>150</v>
@@ -35083,7 +35084,7 @@
         <v>227</v>
       </c>
       <c r="P36" s="110" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="Q36" s="60" t="n">
         <v>25862</v>
@@ -35185,7 +35186,7 @@
         <v>929</v>
       </c>
       <c r="L37" s="110" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="M37" s="36" t="s">
         <v>150</v>
@@ -35197,7 +35198,7 @@
         <v>151</v>
       </c>
       <c r="P37" s="110" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="Q37" s="60" t="n">
         <v>29694</v>
@@ -35295,10 +35296,10 @@
         <v>106</v>
       </c>
       <c r="K38" s="110" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L38" s="110" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="M38" s="36" t="s">
         <v>114</v>
@@ -35310,7 +35311,7 @@
         <v>408</v>
       </c>
       <c r="P38" s="110" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="Q38" s="60" t="n">
         <v>26099</v>
@@ -35325,23 +35326,23 @@
         <v>120</v>
       </c>
       <c r="V38" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X38" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y38" s="110"/>
       <c r="Z38" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="AA38" s="10" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AB38" s="43" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="AC38" s="4" t="n">
         <v>45616</v>
@@ -35436,10 +35437,10 @@
         <v>106</v>
       </c>
       <c r="K39" s="110" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="M39" s="36" t="s">
         <v>150</v>
@@ -35451,7 +35452,7 @@
         <v>548</v>
       </c>
       <c r="P39" s="110" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="Q39" s="60" t="n">
         <v>30878</v>
@@ -35466,16 +35467,16 @@
         <v>120</v>
       </c>
       <c r="V39" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X39" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y39" s="110" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="Z39" s="9" t="n">
         <v>45615</v>
@@ -35484,7 +35485,7 @@
         <v>936</v>
       </c>
       <c r="AB39" s="43" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="AC39" s="4" t="n">
         <v>45616</v>
@@ -35582,10 +35583,10 @@
         <v>106</v>
       </c>
       <c r="K40" s="110" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M40" s="36" t="s">
         <v>150</v>
@@ -35597,7 +35598,7 @@
         <v>402</v>
       </c>
       <c r="P40" s="110" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="Q40" s="60" t="n">
         <v>30466</v>
@@ -35612,16 +35613,16 @@
         <v>120</v>
       </c>
       <c r="V40" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X40" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y40" s="110" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="Z40" s="9" t="n">
         <v>45615</v>
@@ -35630,7 +35631,7 @@
         <v>936</v>
       </c>
       <c r="AB40" s="43" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="AC40" s="4" t="n">
         <v>45616</v>
@@ -35728,22 +35729,22 @@
         <v>106</v>
       </c>
       <c r="K41" s="110" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="M41" s="36" t="s">
         <v>114</v>
       </c>
       <c r="N41" s="110" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O41" s="110" t="s">
         <v>408</v>
       </c>
       <c r="P41" s="110" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="Q41" s="60" t="n">
         <v>35345</v>
@@ -35758,25 +35759,25 @@
         <v>120</v>
       </c>
       <c r="V41" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X41" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y41" s="110" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="Z41" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA41" s="10" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AB41" s="43" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AC41" s="4" t="n">
         <v>45616</v>
@@ -35901,22 +35902,22 @@
         <v>106</v>
       </c>
       <c r="K42" s="110" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M42" s="36" t="s">
         <v>150</v>
       </c>
       <c r="N42" s="110" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O42" s="110" t="s">
         <v>408</v>
       </c>
       <c r="P42" s="110" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="Q42" s="60" t="n">
         <v>25193</v>
@@ -35931,16 +35932,16 @@
         <v>120</v>
       </c>
       <c r="V42" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W42" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X42" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y42" s="110" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="Z42" s="9" t="n">
         <v>45616</v>
@@ -35949,7 +35950,7 @@
         <v>955</v>
       </c>
       <c r="AB42" s="43" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AC42" s="4" t="n">
         <v>45617</v>
@@ -36074,22 +36075,22 @@
         <v>106</v>
       </c>
       <c r="K43" s="110" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M43" s="36" t="s">
         <v>150</v>
       </c>
       <c r="N43" s="110" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O43" s="110" t="s">
         <v>408</v>
       </c>
       <c r="P43" s="110" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="Q43" s="60" t="n">
         <v>21513</v>
@@ -36104,16 +36105,16 @@
         <v>120</v>
       </c>
       <c r="V43" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X43" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y43" s="110" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="Z43" s="9" t="n">
         <v>45616</v>
@@ -36122,7 +36123,7 @@
         <v>955</v>
       </c>
       <c r="AB43" s="43" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AC43" s="4" t="n">
         <v>45617</v>
@@ -36247,10 +36248,10 @@
         <v>106</v>
       </c>
       <c r="K44" s="110" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="M44" s="36" t="s">
         <v>150</v>
@@ -36262,7 +36263,7 @@
         <v>239</v>
       </c>
       <c r="P44" s="110" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="Q44" s="60" t="n">
         <v>31770</v>
@@ -36277,16 +36278,16 @@
         <v>120</v>
       </c>
       <c r="V44" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X44" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y44" s="110" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="Z44" s="9" t="n">
         <v>45616</v>
@@ -36295,7 +36296,7 @@
         <v>909</v>
       </c>
       <c r="AB44" s="43" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AC44" s="4" t="n">
         <v>45616</v>
@@ -36420,10 +36421,10 @@
         <v>106</v>
       </c>
       <c r="K45" s="110" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="M45" s="36" t="s">
         <v>150</v>
@@ -36435,7 +36436,7 @@
         <v>438</v>
       </c>
       <c r="P45" s="110" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="Q45" s="60" t="n">
         <v>34366</v>
@@ -36450,16 +36451,16 @@
         <v>120</v>
       </c>
       <c r="V45" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X45" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y45" s="110" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="Z45" s="9" t="n">
         <v>45616</v>
@@ -36468,7 +36469,7 @@
         <v>909</v>
       </c>
       <c r="AB45" s="43" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AC45" s="4" t="n">
         <v>45616</v>
@@ -36593,10 +36594,10 @@
         <v>106</v>
       </c>
       <c r="K46" s="110" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M46" s="36" t="s">
         <v>150</v>
@@ -36608,7 +36609,7 @@
         <v>425</v>
       </c>
       <c r="P46" s="110" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="Q46" s="60" t="n">
         <v>35627</v>
@@ -36623,25 +36624,25 @@
         <v>120</v>
       </c>
       <c r="V46" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X46" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y46" s="110" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="Z46" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA46" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB46" s="43" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AC46" s="4" t="n">
         <v>45616</v>
@@ -36766,10 +36767,10 @@
         <v>106</v>
       </c>
       <c r="K47" s="110" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="M47" s="36" t="s">
         <v>150</v>
@@ -36781,7 +36782,7 @@
         <v>558</v>
       </c>
       <c r="P47" s="110" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="Q47" s="60" t="n">
         <v>36699</v>
@@ -36796,25 +36797,25 @@
         <v>120</v>
       </c>
       <c r="V47" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W47" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X47" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y47" s="110" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Z47" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA47" s="10" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AB47" s="43" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AC47" s="4" t="n">
         <v>45616</v>
@@ -36939,22 +36940,22 @@
         <v>106</v>
       </c>
       <c r="K48" s="110" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="M48" s="36" t="s">
         <v>150</v>
       </c>
       <c r="N48" s="110" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="O48" s="110" t="s">
         <v>408</v>
       </c>
       <c r="P48" s="110" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="Q48" s="60" t="n">
         <v>33466</v>
@@ -36969,25 +36970,25 @@
         <v>120</v>
       </c>
       <c r="V48" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X48" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y48" s="110" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="Z48" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA48" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB48" s="43" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AC48" s="4" t="n">
         <v>45616</v>
@@ -37112,10 +37113,10 @@
         <v>106</v>
       </c>
       <c r="K49" s="110" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="M49" s="36" t="s">
         <v>150</v>
@@ -37127,7 +37128,7 @@
         <v>455</v>
       </c>
       <c r="P49" s="110" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="Q49" s="60" t="n">
         <v>32481</v>
@@ -37142,25 +37143,25 @@
         <v>120</v>
       </c>
       <c r="V49" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X49" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y49" s="110" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Z49" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA49" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AB49" s="43" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AC49" s="4" t="n">
         <v>45616</v>
@@ -37285,10 +37286,10 @@
         <v>106</v>
       </c>
       <c r="K50" s="110" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="M50" s="36" t="s">
         <v>150</v>
@@ -37300,7 +37301,7 @@
         <v>483</v>
       </c>
       <c r="P50" s="110" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="Q50" s="60" t="n">
         <v>33927</v>
@@ -37315,25 +37316,25 @@
         <v>120</v>
       </c>
       <c r="V50" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X50" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y50" s="110" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Z50" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA50" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AB50" s="43" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AC50" s="4" t="n">
         <v>45616</v>
@@ -37458,10 +37459,10 @@
         <v>106</v>
       </c>
       <c r="K51" s="110" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="M51" s="36" t="s">
         <v>114</v>
@@ -37473,7 +37474,7 @@
         <v>343</v>
       </c>
       <c r="P51" s="110" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="Q51" s="60" t="n">
         <v>32398</v>
@@ -37488,25 +37489,25 @@
         <v>120</v>
       </c>
       <c r="V51" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X51" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y51" s="110" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Z51" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA51" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AB51" s="43" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AC51" s="4" t="n">
         <v>45616</v>
@@ -37631,10 +37632,10 @@
         <v>106</v>
       </c>
       <c r="K52" s="110" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="L52" s="5" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="M52" s="36" t="s">
         <v>150</v>
@@ -37646,7 +37647,7 @@
         <v>334</v>
       </c>
       <c r="P52" s="110" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="Q52" s="60" t="n">
         <v>33314</v>
@@ -37661,25 +37662,25 @@
         <v>120</v>
       </c>
       <c r="V52" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X52" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y52" s="110" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Z52" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA52" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AB52" s="43" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AC52" s="4" t="n">
         <v>45616</v>
@@ -37804,10 +37805,10 @@
         <v>106</v>
       </c>
       <c r="K53" s="110" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="L53" s="5" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="M53" s="36" t="s">
         <v>150</v>
@@ -37819,7 +37820,7 @@
         <v>210</v>
       </c>
       <c r="P53" s="110" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="Q53" s="60" t="n">
         <v>33838</v>
@@ -37834,25 +37835,25 @@
         <v>120</v>
       </c>
       <c r="V53" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X53" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y53" s="110" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Z53" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA53" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AB53" s="43" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AC53" s="4" t="n">
         <v>45616</v>
@@ -37977,10 +37978,10 @@
         <v>106</v>
       </c>
       <c r="K54" s="110" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="L54" s="5" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="M54" s="36" t="s">
         <v>150</v>
@@ -37992,7 +37993,7 @@
         <v>164</v>
       </c>
       <c r="P54" s="110" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="Q54" s="60" t="n">
         <v>27871</v>
@@ -38007,25 +38008,25 @@
         <v>120</v>
       </c>
       <c r="V54" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X54" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y54" s="110" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Z54" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA54" s="10" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="AB54" s="43" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="AC54" s="4" t="n">
         <v>45616</v>
@@ -38150,22 +38151,22 @@
         <v>106</v>
       </c>
       <c r="K55" s="110" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="L55" s="5" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M55" s="36" t="s">
         <v>114</v>
       </c>
       <c r="N55" s="110" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="O55" s="110" t="s">
         <v>571</v>
       </c>
       <c r="P55" s="110" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="Q55" s="60" t="n">
         <v>26518</v>
@@ -38180,25 +38181,25 @@
         <v>120</v>
       </c>
       <c r="V55" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X55" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y55" s="110" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="Z55" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA55" s="10" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AB55" s="43" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AC55" s="4" t="n">
         <v>45616</v>
@@ -38323,22 +38324,22 @@
         <v>106</v>
       </c>
       <c r="K56" s="110" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="L56" s="5" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="M56" s="36" t="s">
         <v>114</v>
       </c>
       <c r="N56" s="110" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="O56" s="110" t="s">
         <v>402</v>
       </c>
       <c r="P56" s="110" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="Q56" s="60" t="n">
         <v>33209</v>
@@ -38353,25 +38354,25 @@
         <v>120</v>
       </c>
       <c r="V56" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X56" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y56" s="110" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="Z56" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA56" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB56" s="43" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="AC56" s="4" t="n">
         <v>45616</v>
@@ -38496,10 +38497,10 @@
         <v>106</v>
       </c>
       <c r="K57" s="110" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="L57" s="5" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="M57" s="36" t="s">
         <v>150</v>
@@ -38511,7 +38512,7 @@
         <v>408</v>
       </c>
       <c r="P57" s="110" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="Q57" s="60" t="n">
         <v>33609</v>
@@ -38526,16 +38527,16 @@
         <v>540</v>
       </c>
       <c r="V57" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X57" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y57" s="110" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Z57" s="9" t="n">
         <v>45615</v>
@@ -38544,7 +38545,7 @@
         <v>955</v>
       </c>
       <c r="AB57" s="43" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AC57" s="4" t="n">
         <v>45616</v>
@@ -38638,10 +38639,10 @@
         <v>106</v>
       </c>
       <c r="K58" s="110" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="L58" s="5" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="M58" s="36" t="s">
         <v>114</v>
@@ -38653,7 +38654,7 @@
         <v>448</v>
       </c>
       <c r="P58" s="110" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="Q58" s="60" t="n">
         <v>33431</v>
@@ -38668,16 +38669,16 @@
         <v>540</v>
       </c>
       <c r="V58" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X58" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y58" s="110" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="Z58" s="9" t="n">
         <v>45615</v>
@@ -38686,7 +38687,7 @@
         <v>955</v>
       </c>
       <c r="AB58" s="43" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AC58" s="4" t="n">
         <v>45616</v>
@@ -38780,10 +38781,10 @@
         <v>106</v>
       </c>
       <c r="K59" s="110" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="M59" s="36" t="s">
         <v>114</v>
@@ -38795,7 +38796,7 @@
         <v>408</v>
       </c>
       <c r="P59" s="110" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="Q59" s="60" t="n">
         <v>34823</v>
@@ -38810,25 +38811,25 @@
         <v>120</v>
       </c>
       <c r="V59" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X59" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y59" s="110" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="Z59" s="9" t="n">
         <v>45616</v>
       </c>
       <c r="AA59" s="10" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AB59" s="43" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="AC59" s="4" t="n">
         <v>45616</v>
@@ -38953,22 +38954,22 @@
         <v>106</v>
       </c>
       <c r="K60" s="110" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="M60" s="36" t="s">
         <v>114</v>
       </c>
       <c r="N60" s="110" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="O60" s="110" t="s">
         <v>408</v>
       </c>
       <c r="P60" s="110" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="Q60" s="60" t="n">
         <v>23531</v>
@@ -38983,16 +38984,16 @@
         <v>600</v>
       </c>
       <c r="V60" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X60" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y60" s="110" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="Z60" s="9" t="n">
         <v>45615</v>
@@ -39001,7 +39002,7 @@
         <v>936</v>
       </c>
       <c r="AB60" s="43" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="AC60" s="4" t="n">
         <v>45616</v>
@@ -39043,7 +39044,7 @@
         <v>138</v>
       </c>
       <c r="AP60" s="10" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="BA60" s="61" t="s">
         <v>143</v>
@@ -39134,10 +39135,10 @@
         <v>106</v>
       </c>
       <c r="K61" s="130" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="L61" s="76" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="M61" s="49" t="s">
         <v>114</v>
@@ -39149,7 +39150,7 @@
         <v>708</v>
       </c>
       <c r="P61" s="130" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="Q61" s="129" t="n">
         <v>35127</v>
@@ -39164,13 +39165,13 @@
         <v>119</v>
       </c>
       <c r="V61" s="58" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W61" s="86" t="n">
         <v>45615</v>
       </c>
       <c r="X61" s="131" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y61" s="130" t="s">
         <v>941</v>
@@ -39182,7 +39183,7 @@
         <v>0.999305555555556</v>
       </c>
       <c r="AB61" s="58" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AC61" s="77" t="n">
         <v>45616</v>
@@ -39293,10 +39294,10 @@
         <v>106</v>
       </c>
       <c r="K62" s="110" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="M62" s="36" t="s">
         <v>150</v>
@@ -39308,7 +39309,7 @@
         <v>294</v>
       </c>
       <c r="P62" s="110" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="Q62" s="60" t="n">
         <v>30583</v>
@@ -39323,16 +39324,16 @@
         <v>119</v>
       </c>
       <c r="V62" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X62" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y62" s="110" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="Z62" s="9" t="n">
         <v>45615</v>
@@ -39341,7 +39342,7 @@
         <v>950</v>
       </c>
       <c r="AB62" s="43" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AC62" s="4" t="n">
         <v>45616</v>
@@ -39383,7 +39384,7 @@
         <v>138</v>
       </c>
       <c r="AP62" s="10" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="BA62" s="61" t="s">
         <v>143</v>
@@ -39475,10 +39476,10 @@
         <v>106</v>
       </c>
       <c r="K63" s="110" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="L63" s="5" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="M63" s="36" t="s">
         <v>150</v>
@@ -39490,7 +39491,7 @@
         <v>116</v>
       </c>
       <c r="P63" s="110" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="Q63" s="60" t="n">
         <v>35635</v>
@@ -39505,16 +39506,16 @@
         <v>540</v>
       </c>
       <c r="V63" s="43" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X63" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y63" s="110" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="Z63" s="9" t="n">
         <v>45616</v>
@@ -39604,7 +39605,7 @@
         <v>141</v>
       </c>
       <c r="BQ63" s="62" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="BR63" s="67" t="n">
         <v>0.916666666666667</v>
@@ -39645,10 +39646,10 @@
         <v>106</v>
       </c>
       <c r="K64" s="110" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="L64" s="5" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="M64" s="36" t="s">
         <v>150</v>
@@ -39657,10 +39658,10 @@
         <v>262</v>
       </c>
       <c r="O64" s="110" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="P64" s="110" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="Q64" s="60" t="n">
         <v>28169</v>
@@ -39675,13 +39676,13 @@
         <v>466</v>
       </c>
       <c r="V64" s="43" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>45615</v>
       </c>
       <c r="X64" s="7" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="Y64" s="110" t="s">
         <v>914</v>
@@ -39690,10 +39691,10 @@
         <v>45615</v>
       </c>
       <c r="AA64" s="10" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AB64" s="43" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="AC64" s="4" t="n">
         <v>45616</v>
@@ -39809,22 +39810,22 @@
         <v>106</v>
       </c>
       <c r="K65" s="43" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="L65" s="10" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="M65" s="36" t="s">
         <v>150</v>
       </c>
       <c r="N65" s="110" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="O65" s="110" t="s">
         <v>779</v>
       </c>
       <c r="P65" s="110" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>34570</v>
@@ -39839,31 +39840,31 @@
         <v>119</v>
       </c>
       <c r="V65" s="43" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X65" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y65" s="110" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="Z65" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="AA65" s="10" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="AB65" s="10" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AC65" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD65" s="113" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="AE65" s="37" t="s">
         <v>132</v>
@@ -39950,10 +39951,10 @@
         <v>106</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="L66" s="10" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>150</v>
@@ -39980,31 +39981,31 @@
         <v>312</v>
       </c>
       <c r="V66" s="43" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X66" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y66" s="110" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="Z66" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="AA66" s="10" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="AB66" s="10" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AC66" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD66" s="113" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="AE66" s="37" t="s">
         <v>132</v>
@@ -40095,22 +40096,22 @@
         <v>106</v>
       </c>
       <c r="K67" s="10" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="L67" s="10" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N67" s="5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="O67" s="5" t="s">
         <v>763</v>
       </c>
       <c r="P67" s="5" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>33373</v>
@@ -40125,31 +40126,31 @@
         <v>119</v>
       </c>
       <c r="V67" s="43" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X67" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y67" s="110" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="Z67" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA67" s="10" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="AB67" s="10" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="AC67" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD67" s="113" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="AE67" s="37" t="s">
         <v>132</v>
@@ -40251,10 +40252,10 @@
         <v>106</v>
       </c>
       <c r="K68" s="10" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="L68" s="10" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>150</v>
@@ -40266,7 +40267,7 @@
         <v>425</v>
       </c>
       <c r="P68" s="5" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="Q68" s="9" t="n">
         <v>34881</v>
@@ -40281,31 +40282,31 @@
         <v>119</v>
       </c>
       <c r="V68" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X68" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y68" s="5" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="Z68" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA68" s="10" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AB68" s="10" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AC68" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD68" s="113" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AE68" s="37" t="s">
         <v>132</v>
@@ -40410,22 +40411,22 @@
         <v>106</v>
       </c>
       <c r="K69" s="10" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="L69" s="10" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N69" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O69" s="5" t="s">
         <v>359</v>
       </c>
       <c r="P69" s="5" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>33949</v>
@@ -40440,31 +40441,31 @@
         <v>119</v>
       </c>
       <c r="V69" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X69" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y69" s="5" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="Z69" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA69" s="10" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AB69" s="10" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AC69" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD69" s="113" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AE69" s="37" t="s">
         <v>132</v>
@@ -40569,22 +40570,22 @@
         <v>106</v>
       </c>
       <c r="K70" s="10" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="L70" s="10" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N70" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O70" s="5" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="P70" s="5" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>24371</v>
@@ -40599,31 +40600,31 @@
         <v>410</v>
       </c>
       <c r="V70" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X70" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y70" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Z70" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA70" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB70" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AC70" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD70" s="97" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AE70" s="37" t="s">
         <v>132</v>
@@ -40728,22 +40729,22 @@
         <v>106</v>
       </c>
       <c r="K71" s="10" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="L71" s="10" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>114</v>
       </c>
       <c r="N71" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O71" s="5" t="s">
         <v>834</v>
       </c>
       <c r="P71" s="5" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>30318</v>
@@ -40758,31 +40759,31 @@
         <v>410</v>
       </c>
       <c r="V71" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X71" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y71" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Z71" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA71" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB71" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AC71" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD71" s="97" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AE71" s="37" t="s">
         <v>132</v>
@@ -40887,22 +40888,22 @@
         <v>106</v>
       </c>
       <c r="K72" s="10" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="L72" s="10" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N72" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O72" s="5" t="s">
         <v>717</v>
       </c>
       <c r="P72" s="5" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>30106</v>
@@ -40917,31 +40918,31 @@
         <v>410</v>
       </c>
       <c r="V72" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X72" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y72" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Z72" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA72" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB72" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AC72" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD72" s="97" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AE72" s="37" t="s">
         <v>132</v>
@@ -41046,22 +41047,22 @@
         <v>106</v>
       </c>
       <c r="K73" s="10" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="L73" s="10" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N73" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O73" s="5" t="s">
         <v>294</v>
       </c>
       <c r="P73" s="5" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>31510</v>
@@ -41076,31 +41077,31 @@
         <v>410</v>
       </c>
       <c r="V73" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X73" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y73" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Z73" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA73" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB73" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AC73" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD73" s="97" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AE73" s="37" t="s">
         <v>132</v>
@@ -41205,22 +41206,22 @@
         <v>106</v>
       </c>
       <c r="K74" s="10" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="L74" s="10" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="M74" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N74" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O74" s="5" t="s">
         <v>730</v>
       </c>
       <c r="P74" s="5" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="Q74" s="9" t="n">
         <v>26595</v>
@@ -41235,31 +41236,31 @@
         <v>410</v>
       </c>
       <c r="V74" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X74" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y74" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Z74" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA74" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB74" s="10" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="AC74" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD74" s="97" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="AE74" s="37" t="s">
         <v>132</v>
@@ -41364,16 +41365,16 @@
         <v>106</v>
       </c>
       <c r="K75" s="10" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="L75" s="10" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N75" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="O75" s="5" t="s">
         <v>786</v>
@@ -41394,31 +41395,31 @@
         <v>312</v>
       </c>
       <c r="V75" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X75" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y75" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="Z75" s="9" t="n">
         <v>45626</v>
       </c>
       <c r="AA75" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB75" s="10" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AC75" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD75" s="97" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="AE75" s="37" t="s">
         <v>132</v>
@@ -41454,7 +41455,7 @@
         <v>176</v>
       </c>
       <c r="AP75" s="10" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="BA75" s="1" t="s">
         <v>143</v>
@@ -41523,10 +41524,10 @@
         <v>106</v>
       </c>
       <c r="K76" s="10" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="L76" s="10" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>150</v>
@@ -41538,7 +41539,7 @@
         <v>116</v>
       </c>
       <c r="P76" s="5" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>34906</v>
@@ -41553,7 +41554,7 @@
         <v>119</v>
       </c>
       <c r="V76" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>45625</v>
@@ -41568,7 +41569,7 @@
         <v>45626</v>
       </c>
       <c r="AA76" s="10" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AB76" s="10" t="s">
         <v>932</v>
@@ -41577,7 +41578,7 @@
         <v>45626</v>
       </c>
       <c r="AD76" s="97" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="AE76" s="37" t="s">
         <v>132</v>
@@ -41679,22 +41680,22 @@
         <v>106</v>
       </c>
       <c r="K77" s="10" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="L77" s="10" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>150</v>
       </c>
       <c r="N77" s="5" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="O77" s="5" t="s">
         <v>812</v>
       </c>
       <c r="P77" s="5" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>34260</v>
@@ -41709,31 +41710,31 @@
         <v>119</v>
       </c>
       <c r="V77" s="10" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="X77" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="Y77" s="5" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="Z77" s="9" t="n">
         <v>45625</v>
       </c>
       <c r="AA77" s="10" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="AB77" s="10" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="AC77" s="4" t="n">
         <v>45626</v>
       </c>
       <c r="AD77" s="97" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="AE77" s="37" t="s">
         <v>132</v>

--- a/Carga_Real_FRAM Apply-Actualizado 28-11.xlsx
+++ b/Carga_Real_FRAM Apply-Actualizado 28-11.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7817" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7816" uniqueCount="1199">
   <si>
     <t xml:space="preserve">Activo</t>
   </si>
@@ -13586,8 +13586,8 @@
       <c r="AI38" s="38" t="n">
         <v>45610</v>
       </c>
-      <c r="AJ38" s="41" t="s">
-        <v>235</v>
+      <c r="AJ38" s="41" t="n">
+        <v>0.597222222222222</v>
       </c>
       <c r="AK38" s="44" t="s">
         <v>305</v>
